--- a/cp_add-precision-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/cp_add-precision-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:46+00:00</t>
+    <t>2026-06-03T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
